--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -781,6 +781,226 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>123877711</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58322</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kilanda - Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>338587</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6418584</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stora Lundby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Matilda Gille</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Matilda Gille, Anneli Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdeinventering Kilanda-Stenkullen 2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123877797</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58350</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kilanda - Stenkullen, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>338587</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6418584</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lerum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stora Lundby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Matilda Gille</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Matilda Gille, Lisa Werthén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdeinventering Kilanda-Stenkullen 2024</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
         <v>123877711</v>
       </c>
       <c r="B3" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>123877797</v>
       </c>
       <c r="B4" t="n">
-        <v>58350</v>
+        <v>58351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Gille, Lisa Werthén</t>
+          <t>Lisa Werthén, Matilda Gille</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Werthén, Matilda Gille</t>
+          <t>Matilda Gille, Lisa Werthén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877711</v>
+        <v>123877797</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>58351</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Gille, Anneli Nilsson</t>
+          <t>Matilda Gille, Lisa Werthén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877797</v>
+        <v>123877711</v>
       </c>
       <c r="B4" t="n">
-        <v>58351</v>
+        <v>58323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Gille, Lisa Werthén</t>
+          <t>Matilda Gille, Anneli Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877797</v>
+        <v>123877711</v>
       </c>
       <c r="B3" t="n">
-        <v>58351</v>
+        <v>58323</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Gille, Lisa Werthén</t>
+          <t>Matilda Gille, Anneli Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877711</v>
+        <v>123877797</v>
       </c>
       <c r="B4" t="n">
-        <v>58323</v>
+        <v>58351</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Gille, Anneli Nilsson</t>
+          <t>Matilda Gille, Lisa Werthén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877711</v>
+        <v>123877797</v>
       </c>
       <c r="B3" t="n">
-        <v>58345</v>
+        <v>58373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Gille, Anneli Nilsson</t>
+          <t>Matilda Gille, Lisa Werthén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877797</v>
+        <v>123877711</v>
       </c>
       <c r="B4" t="n">
-        <v>58373</v>
+        <v>58345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Gille, Lisa Werthén</t>
+          <t>Matilda Gille, Anneli Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877797</v>
+        <v>123877711</v>
       </c>
       <c r="B3" t="n">
-        <v>58373</v>
+        <v>58345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Gille, Lisa Werthén</t>
+          <t>Matilda Gille, Anneli Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877711</v>
+        <v>123877797</v>
       </c>
       <c r="B4" t="n">
-        <v>58345</v>
+        <v>58373</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Matilda Gille, Anneli Nilsson</t>
+          <t>Lisa Werthén, Matilda Gille</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 12259-2025 artfynd.xlsx
+++ b/artfynd/A 12259-2025 artfynd.xlsx
@@ -784,10 +784,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123877711</v>
+        <v>123877797</v>
       </c>
       <c r="B3" t="n">
-        <v>58345</v>
+        <v>58373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -800,21 +800,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Matilda Gille, Anneli Nilsson</t>
+          <t>Matilda Gille, Lisa Werthén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123877797</v>
+        <v>123877711</v>
       </c>
       <c r="B4" t="n">
-        <v>58373</v>
+        <v>58345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,21 +910,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208249</v>
+        <v>208245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Werthén, Matilda Gille</t>
+          <t>Matilda Gille, Anneli Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
